--- a/branches/dev/mii-cm-onko-therapie-typ-sct.xlsx
+++ b/branches/dev/mii-cm-onko-therapie-typ-sct.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2026.0.3</t>
+    <t>2027.0.0-ballot.rc1</t>
   </si>
   <si>
     <t>Name</t>
@@ -153,42 +153,45 @@
     <t>Immun-/Antikörpertherapie</t>
   </si>
   <si>
+    <t>76334006</t>
+  </si>
+  <si>
+    <t>Immunotherapy (procedure)</t>
+  </si>
+  <si>
+    <t>ZS</t>
+  </si>
+  <si>
+    <t>zielgerichtete Substanzen</t>
+  </si>
+  <si>
+    <t>1255831008</t>
+  </si>
+  <si>
+    <t>Chemotherapy for malignant neoplastic disease using targeted agent (procedure)</t>
+  </si>
+  <si>
+    <t>SZ</t>
+  </si>
+  <si>
+    <t>Stammzelltransplantation (inklusive Knochenmarktransplantation)</t>
+  </si>
+  <si>
+    <t>1269349006</t>
+  </si>
+  <si>
+    <t>Transplantation of stem cell (procedure)</t>
+  </si>
+  <si>
+    <t>CI</t>
+  </si>
+  <si>
+    <t>Chemo- + Immun-/Antikörpertherapie</t>
+  </si>
+  <si>
     <t>897713009</t>
   </si>
   <si>
-    <t>Immunotherapy (procedure)</t>
-  </si>
-  <si>
-    <t>ZS</t>
-  </si>
-  <si>
-    <t>zielgerichtete Substanzen</t>
-  </si>
-  <si>
-    <t>1255831008</t>
-  </si>
-  <si>
-    <t>Chemotherapy for malignant neoplastic disease using targeted agent (procedure)</t>
-  </si>
-  <si>
-    <t>SZ</t>
-  </si>
-  <si>
-    <t>Stammzelltransplantation (inklusive Knochenmarktransplantation)</t>
-  </si>
-  <si>
-    <t>1269349006</t>
-  </si>
-  <si>
-    <t>Transplantation of stem cell (procedure)</t>
-  </si>
-  <si>
-    <t>CI</t>
-  </si>
-  <si>
-    <t>Chemo- + Immun-/Antikörpertherapie</t>
-  </si>
-  <si>
     <t>Antineoplastic chemoimmunotherapy (regime/therapy)</t>
   </si>
   <si>
@@ -211,9 +214,6 @@
   </si>
   <si>
     <t>Immun-/Antikörpertherapie + zielgerichtete Substanzen</t>
-  </si>
-  <si>
-    <t>76334006</t>
   </si>
   <si>
     <t>WW</t>
@@ -706,18 +706,18 @@
         <v>37</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="E8" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C9" t="s" s="2">
         <v>37</v>
@@ -731,26 +731,26 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="E10" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D11" t="s" s="2">
         <v>50</v>
@@ -761,16 +761,16 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="C12" t="s" s="2">
         <v>64</v>
       </c>
-      <c r="B12" t="s" s="2">
-        <v>65</v>
-      </c>
-      <c r="C12" t="s" s="2">
-        <v>63</v>
-      </c>
       <c r="D12" t="s" s="2">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="E12" t="s" s="2">
         <v>47</v>
@@ -780,7 +780,7 @@
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D13" t="s" s="2">
         <v>50</v>

--- a/branches/dev/mii-cm-onko-therapie-typ-sct.xlsx
+++ b/branches/dev/mii-cm-onko-therapie-typ-sct.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc1</t>
+    <t>2027.0.0-ballot.rc2</t>
   </si>
   <si>
     <t>Name</t>
